--- a/output/私立高校_Web出願_進捗管理.xlsx
+++ b/output/私立高校_Web出願_進捗管理.xlsx
@@ -574,18 +574,18 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8.5" customWidth="1" min="5" max="5"/>
-    <col width="8.5" customWidth="1" min="6" max="6"/>
-    <col width="8.5" customWidth="1" min="7" max="7"/>
-    <col width="8.5" customWidth="1" min="8" max="8"/>
-    <col width="8.5" customWidth="1" min="9" max="9"/>
-    <col width="8.5" customWidth="1" min="10" max="10"/>
-    <col width="8.5" customWidth="1" min="11" max="11"/>
-    <col width="8.5" customWidth="1" min="12" max="12"/>
-    <col width="8.5" customWidth="1" min="13" max="13"/>
-    <col width="8.5" customWidth="1" min="14" max="14"/>
-    <col width="8.5" customWidth="1" min="15" max="15"/>
-    <col width="8.5" customWidth="1" min="16" max="16"/>
+    <col width="10.5" customWidth="1" min="5" max="5"/>
+    <col width="10.5" customWidth="1" min="6" max="6"/>
+    <col width="10.5" customWidth="1" min="7" max="7"/>
+    <col width="10.5" customWidth="1" min="8" max="8"/>
+    <col width="10.5" customWidth="1" min="9" max="9"/>
+    <col width="10.5" customWidth="1" min="10" max="10"/>
+    <col width="10.5" customWidth="1" min="11" max="11"/>
+    <col width="10.5" customWidth="1" min="12" max="12"/>
+    <col width="10.5" customWidth="1" min="13" max="13"/>
+    <col width="10.5" customWidth="1" min="14" max="14"/>
+    <col width="10.5" customWidth="1" min="15" max="15"/>
+    <col width="10.5" customWidth="1" min="16" max="16"/>
     <col width="7" customWidth="1" min="17" max="17"/>
     <col width="8" customWidth="1" min="18" max="18"/>
   </cols>
@@ -604,7 +604,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
+    <row r="4" ht="56" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>番号</t>
@@ -627,62 +627,74 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>受験校決定</t>
+          <t>住所確認
+11/20</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>要項確認</t>
+          <t>説明会
+11/27</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>メール登録</t>
+          <t>手書き下書き
+11/27</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>写真データ</t>
+          <t>オンライン下書き
+12/1〜3</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>下書き確認</t>
+          <t>下書き印刷
+12/1〜3</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Web入力完了</t>
+          <t>担当チェック
+12/4</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>受験料支払</t>
+          <t>修正
+12/4〜10</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>担任へ報告</t>
+          <t>出願確定
+12/4〜10</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>入力内容照合</t>
+          <t>受験料支払
+12/4〜10</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>調査書発送</t>
+          <t>志願票等の印刷
+12/4〜10</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>受験票印刷</t>
+          <t>学校へ提出
+12/11</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>受験票確認</t>
+          <t>提出書類確認
+12/11</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -2382,7 +2394,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>1　受験校を決める</t>
+          <t>事前に　受験校を決める</t>
         </is>
       </c>
       <c r="B4" s="7" t="n"/>
@@ -2424,7 +2436,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>受験料・入学金・入学手続の締切（公立の合格発表より前か）を保護者と確認した</t>
+          <t>受験料・入学金・入学手続の締切を保護者と確認した</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2436,7 +2448,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>2　募集要項を確認する</t>
+          <t>住所を確認する</t>
         </is>
       </c>
       <c r="B8" s="7" t="n"/>
@@ -2448,12 +2460,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>今年度の募集要項とインターネット出願マニュアルを手に入れた</t>
+          <t>郵便番号と住所を、番地・建物名・部屋番号まで正確に確認した</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>高校のWebサイト・長崎県私学協会の一覧</t>
+          <t>住民票や保険証などで確認</t>
         </is>
       </c>
     </row>
@@ -2463,14 +2475,10 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>事前入力の開始日・出願期間・受験料の支払期限を確認した</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>上の「受験する高校」の表に書く</t>
-        </is>
-      </c>
+          <t>保護者の氏名（ふりがな）・続柄・電話番号を確認した</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2478,14 +2486,10 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>中学校の校内締切（担任に出願完了を報告する日）を確認した</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>高校の締切より早いことが多い</t>
-        </is>
-      </c>
+          <t>出願に使うメールアドレス（保護者が受け取れるもの）を決めた</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -2493,15 +2497,19 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>試験日・合格発表日・入学手続の締切を確認した</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr"/>
+          <t>自分の氏名・ふりがな・生年月日の正しい書き方を確認した</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>旧字体・外字があれば担任に相談</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>3　出願の準備をする</t>
+          <t>説明を聞き、手書きで下書きする</t>
         </is>
       </c>
       <c r="B13" s="7" t="n"/>
@@ -2513,12 +2521,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>保護者が受け取れるメールアドレスを用意し、出願サイトからのメールを受信できるよう設定した</t>
+          <t>受験する高校の担当の先生から、出願の仕方の説明を聞いた</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>迷惑メール設定に注意</t>
+          <t>募集要項・出願マニュアルを受け取る</t>
         </is>
       </c>
     </row>
@@ -2528,14 +2536,10 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>顔写真のデータを用意した（撮影時期・服装・背景・サイズは要項どおり）</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>正面・無帽・背景は無地</t>
-        </is>
-      </c>
+          <t>受験校の日程を、上の「受験する高校」の表に書いた</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2543,12 +2547,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>出願用の下書きに入力内容を書き、担任に確認してもらった</t>
+          <t>手書きの下書き用紙に、入力する内容をすべて書いた</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>高校が配る下書き用紙を使う</t>
+          <t>11月20日に確認した住所を見て書く</t>
         </is>
       </c>
     </row>
@@ -2558,19 +2562,15 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>入力に使うパソコンやスマートフォンと、印刷の方法を用意した</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>コンビニのプリントも可</t>
-        </is>
-      </c>
+          <t>下書きを家に持ち帰り、保護者に見せて、12月1〜3日の予定を伝えた</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>4　Web出願の入力をする</t>
+          <t>家庭でオンラインの下書きをする</t>
         </is>
       </c>
       <c r="B18" s="7" t="n"/>
@@ -2582,10 +2582,14 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>出願サイトで利用者登録をし、IDとパスワードを控えた</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr"/>
+          <t>出願サイトからのメールを受け取れるように、受信設定をした</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>迷惑メール設定に注意</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2593,7 +2597,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>受験する試験・入試区分・学科・コースを正しく選んだ</t>
+          <t>出願サイトで利用者登録をし、IDとパスワードを控えた</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr"/>
@@ -2604,12 +2608,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>氏名・ふりがな・生年月日を正しく入力した</t>
+          <t>手書きの下書きを見ながら、保護者と一緒に出願内容を入力した</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>外字は要項の指示に従う</t>
+          <t>まだ出願を確定しない</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2623,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>住所・電話番号・緊急連絡先を正しく入力した</t>
+          <t>顔写真のデータを用意してアップロードした</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>番地・建物名・部屋番号も省略しない</t>
+          <t>撮影時期・服装・背景は要項どおり</t>
         </is>
       </c>
     </row>
@@ -2634,95 +2638,95 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>中学校名と卒業見込みの年月を正しく入力した</t>
+          <t>入力した内容（下書き）を印刷した</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>正式名称で入力</t>
+          <t>自宅で印刷できない場合はコンビニのプリントを使う</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>保護者の情報を入力した</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr"/>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>下書きのチェックを受ける</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>顔写真のデータをアップロードした</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr"/>
+          <t>印刷した下書きを学校に持ってきた</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>忘れるとチェックを受けられない</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>担当の先生に下書きをチェックしてもらった</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>入力内容を保護者と一緒に確認してから確定した</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>確定後は修正できないことがある</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>5　受験料を支払う</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>直すところを下書きに赤で書き込み、家に持ち帰った</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>支払方法（クレジットカード・コンビニなど）を選び、期限内に支払った</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr"/>
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>家庭でオンライン出願をする</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>先生に言われたところを直した</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>支払いの控えと出願完了のメールを確認・保存した</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>受付番号を控える</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>6　中学校に報告する</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>保護者と一緒に最終確認をしてから、出願を確定した</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>確定後は直せないことがある</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2730,12 +2734,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>出願が完了したことを担任に報告した（受付番号・受験校・入試区分）</t>
+          <t>受験料を期限内に支払い、支払いの控えを保管した</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>校内締切までに</t>
+          <t>支払方法は高校ごとに確認</t>
         </is>
       </c>
     </row>
@@ -2745,14 +2749,10 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>担任が入力内容を調査書の内容（氏名・生年月日など）と照合した</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>担任が確認</t>
-        </is>
-      </c>
+          <t>出願完了のメールを確認し、受付番号を控えた</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2760,38 +2760,38 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>中学校から高校へ調査書・推薦書などの書類を送った</t>
+          <t>志願票と受験票を、指定された用紙・サイズで印刷した</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>中学校がまとめて送付</t>
+          <t>カラー指定などに注意</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>志願票と受験票を学校へ提出する</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>高校から求められた書類の印刷・提出を終えた</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>必要な場合のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>7　受験票を受け取る</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>印刷した志願票と受験票を学校に提出した</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>12月11日（金）までに</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2799,14 +2799,10 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>受験票を印刷できる日を確認し、印刷した</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>用紙サイズ・カラーの指定に注意</t>
-        </is>
-      </c>
+          <t>受験番号・試験日・試験会場・集合時刻を確認し、メモした</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2814,30 +2810,38 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>受験番号・試験日・試験会場・集合時刻を確認した</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr"/>
+          <t>提出する前に、志願票と受験票のコピーを取った（または写真を撮った）</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>控えとして保管</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>試験の前に</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>受験票をなくさないように保管した（コピーも取った）</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>8　試験の前に</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>受験票の受け取り方と保管の仕方を確認した</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>学校の指示に従う</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2878,14 +2882,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A24:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/私立高校_Web出願_進捗管理.xlsx
+++ b/output/私立高校_Web出願_進捗管理.xlsx
@@ -2359,7 +2359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>手書きの下書き用紙に、入力する内容をすべて書いた</t>
+          <t>受験校の出願期間が、本校の日程（12月4日〜10日に出願）と合っているか確認した</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>11月20日に確認した住所を見て書く</t>
+          <t>違う場合は担当の先生の指示に従う</t>
         </is>
       </c>
     </row>
@@ -2562,34 +2562,34 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
+          <t>手書きの下書き用紙に、入力する内容をすべて書いた</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>11月20日に確認した住所を見て書く</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
           <t>下書きを家に持ち帰り、保護者に見せて、12月1〜3日の予定を伝えた</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>家庭でオンラインの下書きをする</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>出願サイトからのメールを受け取れるように、受信設定をした</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>迷惑メール設定に注意</t>
-        </is>
-      </c>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2597,10 +2597,14 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>出願サイトで利用者登録をし、IDとパスワードを控えた</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr"/>
+          <t>出願サイトからのメールを受け取れるように、受信設定をした</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>迷惑メール設定に注意</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2608,14 +2612,10 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>手書きの下書きを見ながら、保護者と一緒に出願内容を入力した</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>まだ出願を確定しない</t>
-        </is>
-      </c>
+          <t>出願サイトで利用者登録をし、IDとパスワードを控えた</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>顔写真のデータを用意してアップロードした</t>
+          <t>手書きの下書きを見ながら、保護者と一緒に出願内容を入力した</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>撮影時期・服装・背景は要項どおり</t>
+          <t>まだ出願を確定しない</t>
         </is>
       </c>
     </row>
@@ -2638,38 +2638,34 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
+          <t>用意してある顔写真のデータをアップロードした</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
           <t>入力した内容（下書き）を印刷した</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>自宅で印刷できない場合はコンビニのプリントを使う</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>下書きのチェックを受ける</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>印刷した下書きを学校に持ってきた</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>忘れるとチェックを受けられない</t>
-        </is>
-      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2677,10 +2673,14 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>担当の先生に下書きをチェックしてもらった</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr"/>
+          <t>印刷した下書きを学校に持ってきた</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>忘れるとチェックを受けられない</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2688,30 +2688,30 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
+          <t>担当の先生に下書きをチェックしてもらった</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
           <t>直すところを下書きに赤で書き込み、家に持ち帰った</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>家庭でオンライン出願をする</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>先生に言われたところを直した</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2719,14 +2719,10 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>保護者と一緒に最終確認をしてから、出願を確定した</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>確定後は直せないことがある</t>
-        </is>
-      </c>
+          <t>先生に言われたところを直した</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2734,12 +2730,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>受験料を期限内に支払い、支払いの控えを保管した</t>
+          <t>保護者と一緒に最終確認をしてから、出願を確定した</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>支払方法は高校ごとに確認</t>
+          <t>確定後は直せないことがある</t>
         </is>
       </c>
     </row>
@@ -2749,10 +2745,14 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>出願完了のメールを確認し、受付番号を控えた</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr"/>
+          <t>受験料を期限内に支払い、支払いの控えを保管した</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>支払期限は高校ごとに確認</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2760,38 +2760,34 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
+          <t>出願完了のメールを確認し、受付番号を控えた</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
           <t>志願票と受験票を、指定された用紙・サイズで印刷した</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>カラー指定などに注意</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>志願票と受験票を学校へ提出する</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>印刷した志願票と受験票を学校に提出した</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>12月11日（金）までに</t>
-        </is>
-      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2799,10 +2795,14 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>受験番号・試験日・試験会場・集合時刻を確認し、メモした</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr"/>
+          <t>印刷した志願票と受験票を学校に提出した</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>12月11日（金）までに</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2810,38 +2810,34 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
+          <t>受験番号・試験日・試験会場・集合時刻を確認し、メモした</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
           <t>提出する前に、志願票と受験票のコピーを取った（または写真を撮った）</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>控えとして保管</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>試験の前に</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>受験票の受け取り方と保管の仕方を確認した</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>学校の指示に従う</t>
-        </is>
-      </c>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2849,12 +2845,12 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>試験会場までの交通手段と所要時間を確認した</t>
+          <t>学校から返してもらった受験票を、なくさないように保管した</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>天候が悪い日の行き方も考える</t>
+          <t>受験票は試験前に返却されます</t>
         </is>
       </c>
     </row>
@@ -2864,10 +2860,14 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>持ち物（受験票・筆記用具・上履きなど）を確認した</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr"/>
+          <t>試験会場までの交通手段と所要時間を確認した</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>天候が悪い日の行き方も考える</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2875,21 +2875,32 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
+          <t>持ち物（受験票・筆記用具・上履きなど）を確認した</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
           <t>合格後の手続き（入学金の納付・書類提出）の締切を確認した</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr"/>
+      <c r="C43" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A24:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/私立高校_Web出願_進捗管理.xlsx
+++ b/output/私立高校_Web出願_進捗管理.xlsx
@@ -2359,12 +2359,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2390,6 +2391,11 @@
           <t>補足・メモ</t>
         </is>
       </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>先生確認</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -2399,6 +2405,7 @@
       </c>
       <c r="B4" s="7" t="n"/>
       <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2414,6 +2421,11 @@
           <t>公立高校との組み合わせも確認</t>
         </is>
       </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -2429,6 +2441,11 @@
           <t>推薦・専願は合格したら入学が前提</t>
         </is>
       </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -2444,6 +2461,7 @@
           <t>延納制度の有無も確認</t>
         </is>
       </c>
+      <c r="D7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2453,6 +2471,7 @@
       </c>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -2468,6 +2487,11 @@
           <t>住民票や保険証などで確認</t>
         </is>
       </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -2479,6 +2503,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2490,6 +2515,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -2505,6 +2531,11 @@
           <t>旧字体・外字があれば担任に相談</t>
         </is>
       </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2514,6 +2545,7 @@
       </c>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -2529,6 +2561,11 @@
           <t>募集要項・出願マニュアルを受け取る</t>
         </is>
       </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -2540,6 +2577,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2555,6 +2593,11 @@
           <t>違う場合は担当の先生の指示に従う</t>
         </is>
       </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -2570,6 +2613,11 @@
           <t>11月20日に確認した住所を見て書く</t>
         </is>
       </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -2581,6 +2629,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr"/>
+      <c r="D18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -2590,6 +2639,7 @@
       </c>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2605,6 +2655,7 @@
           <t>迷惑メール設定に注意</t>
         </is>
       </c>
+      <c r="D20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2616,6 +2667,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -2631,6 +2683,7 @@
           <t>まだ出願を確定しない</t>
         </is>
       </c>
+      <c r="D22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -2638,10 +2691,15 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>用意してある顔写真のデータをアップロードした</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr"/>
+          <t>写真をアップロードする高校は、用意した顔写真のデータをアップロードした</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>高校によってアップロードか貼り付けかが違う</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -2657,6 +2715,7 @@
           <t>自宅で印刷できない場合はコンビニのプリントを使う</t>
         </is>
       </c>
+      <c r="D24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2666,6 +2725,7 @@
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2681,6 +2741,11 @@
           <t>忘れるとチェックを受けられない</t>
         </is>
       </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2692,6 +2757,11 @@
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2703,6 +2773,7 @@
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -2712,6 +2783,7 @@
       </c>
       <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2723,6 +2795,7 @@
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2738,6 +2811,7 @@
           <t>確定後は直せないことがある</t>
         </is>
       </c>
+      <c r="D31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -2753,6 +2827,7 @@
           <t>支払期限は高校ごとに確認</t>
         </is>
       </c>
+      <c r="D32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2764,6 +2839,7 @@
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2779,30 +2855,33 @@
           <t>カラー指定などに注意</t>
         </is>
       </c>
+      <c r="D34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>写真を貼り付ける高校は、印刷した志願票の指定の場所に写真を貼った</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>のりでしっかり貼る。裏に氏名を書く</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>志願票と受験票を学校へ提出する</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>印刷した志願票と受験票を学校に提出した</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>12月11日（金）までに</t>
-        </is>
-      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2810,10 +2889,19 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>受験番号・試験日・試験会場・集合時刻を確認し、メモした</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr"/>
+          <t>印刷した志願票と受験票を学校に提出した</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>12月11日（金）までに</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2821,38 +2909,41 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
+          <t>受験番号・試験日・試験会場・集合時刻を確認し、メモした</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
           <t>提出する前に、志願票と受験票のコピーを取った（または写真を撮った）</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>控えとして保管</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>試験の前に</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>学校から返してもらった受験票を、なくさないように保管した</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>受験票は試験前に返却されます</t>
-        </is>
-      </c>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2860,12 +2951,17 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>試験会場までの交通手段と所要時間を確認した</t>
+          <t>学校から返してもらった受験票を、なくさないように保管した</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>天候が悪い日の行き方も考える</t>
+          <t>受験票は試験前に返却されます</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -2875,10 +2971,15 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>持ち物（受験票・筆記用具・上履きなど）を確認した</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr"/>
+          <t>試験会場までの交通手段と所要時間を確認した</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>天候が悪い日の行き方も考える</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2886,21 +2987,34 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
+          <t>持ち物（受験票・筆記用具・上履きなど）を確認した</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
           <t>合格後の手続き（入学金の納付・書類提出）の締切を確認した</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr"/>
+      <c r="C44" s="12" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/私立高校_Web出願_進捗管理.xlsx
+++ b/output/私立高校_Web出願_進捗管理.xlsx
@@ -2359,7 +2359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2400,7 +2400,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>事前に　受験校を決める</t>
+          <t>住所を確認する</t>
         </is>
       </c>
       <c r="B4" s="7" t="n"/>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>三者面談で、受験する私立高校・学科・コースを決めた</t>
+          <t>郵便番号と住所を、番地・建物名・部屋番号まで確認した</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>公立高校との組み合わせも確認</t>
+          <t>住民票などで確認</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>入試区分（推薦・専願・一般）を決め、出願の条件を満たしているか確認した</t>
+          <t>氏名・ふりがな・生年月日の正しい書き方を確認した</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>推薦・専願は合格したら入学が前提</t>
+          <t>旧字体・外字は担任に相談</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2453,20 +2453,16 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>受験料・入学金・入学手続の締切を保護者と確認した</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>延納制度の有無も確認</t>
-        </is>
-      </c>
+          <t>保護者の氏名・連絡先と、出願に使うメールアドレスを確認した</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>住所を確認する</t>
+          <t>説明を聞き、手書きで下書きする</t>
         </is>
       </c>
       <c r="B8" s="7" t="n"/>
@@ -2479,14 +2475,10 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>郵便番号と住所を、番地・建物名・部屋番号まで正確に確認した</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>住民票や保険証などで確認</t>
-        </is>
-      </c>
+          <t>担当の先生から出願の仕方の説明を聞き、手書きの下書きを書いた</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>○</t>
@@ -2499,11 +2491,19 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>保護者の氏名（ふりがな）・続柄・電話番号を確認した</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
+          <t>受験校の日程を表に書き、出願期間が本校の日程と合っているか確認した</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>違う場合は先生の指示に従う</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2511,41 +2511,33 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>出願に使うメールアドレス（保護者が受け取れるもの）を決めた</t>
+          <t>下書きを家に持ち帰り、保護者に見せた</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr"/>
       <c r="D11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>家庭でオンラインの下書きをする</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>自分の氏名・ふりがな・生年月日の正しい書き方を確認した</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>旧字体・外字があれば担任に相談</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>説明を聞き、手書きで下書きする</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>メールの受信設定と利用者登録をし、IDとパスワードを控えた</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -2553,19 +2545,15 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>受験する高校の担当の先生から、出願の仕方の説明を聞いた</t>
+          <t>保護者と一緒に出願内容を入力した（写真をアップロードする高校は写真も）</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>募集要項・出願マニュアルを受け取る</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>まだ確定しない</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -2573,154 +2561,150 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>受験校の日程を、上の「受験する高校」の表に書いた</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr"/>
+          <t>入力した内容（下書き）を印刷した</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>コンビニのプリントも可</t>
+        </is>
+      </c>
       <c r="D15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>受験校の出願期間が、本校の日程（12月4日〜10日に出願）と合っているか確認した</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>違う場合は担当の先生の指示に従う</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>下書きのチェックを受ける</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>印刷した下書きを持ってきて、担当の先生にチェックしてもらった</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>直すところを赤で書く</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>家庭でオンライン出願をする</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>手書きの下書き用紙に、入力する内容をすべて書いた</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>11月20日に確認した住所を見て書く</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>下書きを家に持ち帰り、保護者に見せて、12月1〜3日の予定を伝えた</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>家庭でオンラインの下書きをする</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>直すところを直し、保護者と最終確認をして出願を確定した</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>確定後は直せないことがある</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>出願サイトからのメールを受け取れるように、受信設定をした</t>
+          <t>受験料を期限内に支払い、完了メールと受付番号を確認した</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>迷惑メール設定に注意</t>
+          <t>支払期限は高校ごとに確認</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>出願サイトで利用者登録をし、IDとパスワードを控えた</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr"/>
+          <t>志願票と受験票を印刷した（写真を貼る高校は志願票に写真を貼った）</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>用紙・サイズの指定に注意</t>
+        </is>
+      </c>
       <c r="D21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>手書きの下書きを見ながら、保護者と一緒に出願内容を入力した</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>まだ出願を確定しない</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>志願票と受験票を学校へ提出する</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>写真をアップロードする高校は、用意した顔写真のデータをアップロードした</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>高校によってアップロードか貼り付けかが違う</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
+          <t>志願票と受験票のコピーを取り、学校に提出した</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>入力した内容（下書き）を印刷した</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>自宅で印刷できない場合はコンビニのプリントを使う</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
+          <t>受験番号・試験日・試験会場・集合時刻をメモした</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>下書きのチェックを受ける</t>
+          <t>試験の前に</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -2729,16 +2713,16 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>印刷した下書きを学校に持ってきた</t>
+          <t>返してもらった受験票を保管し、交通手段と持ち物を確認した</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>忘れるとチェックを受けられない</t>
+          <t>受験票は試験前に返却</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2747,274 +2731,15 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>担当の先生に下書きをチェックしてもらった</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>直すところを下書きに赤で書き込み、家に持ち帰った</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>家庭でオンライン出願をする</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>先生に言われたところを直した</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>保護者と一緒に最終確認をしてから、出願を確定した</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>確定後は直せないことがある</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>受験料を期限内に支払い、支払いの控えを保管した</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>支払期限は高校ごとに確認</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>出願完了のメールを確認し、受付番号を控えた</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>志願票と受験票を、指定された用紙・サイズで印刷した</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>カラー指定などに注意</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>写真を貼り付ける高校は、印刷した志願票の指定の場所に写真を貼った</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>のりでしっかり貼る。裏に氏名を書く</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>志願票と受験票を学校へ提出する</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>印刷した志願票と受験票を学校に提出した</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>12月11日（金）までに</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>受験番号・試験日・試験会場・集合時刻を確認し、メモした</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>提出する前に、志願票と受験票のコピーを取った（または写真を撮った）</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>控えとして保管</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>試験の前に</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>学校から返してもらった受験票を、なくさないように保管した</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>受験票は試験前に返却されます</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>試験会場までの交通手段と所要時間を確認した</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>天候が悪い日の行き方も考える</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>持ち物（受験票・筆記用具・上履きなど）を確認した</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr"/>
-      <c r="D43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>合格後の手続き（入学金の納付・書類提出）の締切を確認した</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A40:D40"/>
+  <mergeCells count="7">
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/私立高校_Web出願_進捗管理.xlsx
+++ b/output/私立高校_Web出願_進捗管理.xlsx
@@ -2359,7 +2359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2506,26 +2506,26 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>家庭でオンラインの下書きをする</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>下書きを家に持ち帰り、保護者に見せた</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>家庭でオンラインの下書きをする</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="C12" s="12" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -2548,11 +2548,7 @@
           <t>保護者と一緒に出願内容を入力した（写真をアップロードする高校は写真も）</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>まだ確定しない</t>
-        </is>
-      </c>
+      <c r="C14" s="12" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
@@ -2561,71 +2557,71 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
+          <t>受験料はまだ振り込まない（出願も確定しない）</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>12月4日の下書きチェック後に支払う</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
           <t>入力した内容（下書き）を印刷した</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>コンビニのプリントも可</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>下書きのチェックを受ける</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>印刷した下書きを持ってきて、担当の先生にチェックしてもらった</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>直すところを赤で書く</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>家庭でオンライン出願をする</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>直すところを直し、保護者と最終確認をして出願を確定した</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>確定後は直せないことがある</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2633,12 +2629,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>受験料を期限内に支払い、完了メールと受付番号を確認した</t>
+          <t>直すところを直し、保護者と最終確認をして出願を確定した</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>支払期限は高校ごとに確認</t>
+          <t>確定後は直せないことがある</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
@@ -2649,41 +2645,41 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
+          <t>受験料を期限内に支払い、完了メールと受付番号を確認した</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>支払期限は高校ごとに確認</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
           <t>志願票と受験票を印刷した（写真を貼る高校は志願票に写真を貼った）</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>用紙・サイズの指定に注意</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>志願票と受験票を学校へ提出する</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>志願票と受験票のコピーを取り、学校に提出した</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -2691,7 +2687,7 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>受験番号・試験日・試験会場・集合時刻をメモした</t>
+          <t>志願票と受験票のコピーを取り、学校に提出した</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr"/>
@@ -2702,30 +2698,46 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>受験番号・試験日・試験会場・集合時刻をメモした</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>試験の前に</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>返してもらった受験票を保管し、交通手段と持ち物を確認した</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>受験票は試験前に返却</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>○</t>
         </is>
@@ -2733,13 +2745,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/私立高校_Web出願_進捗管理.xlsx
+++ b/output/私立高校_Web出願_進捗管理.xlsx
@@ -2418,7 +2418,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>住民票などで確認</t>
+          <t>夏休みの面談の際に確認した学校からの書類で確認</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
